--- a/For Streamlit.xlsx
+++ b/For Streamlit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2513128\Desktop\Melon Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{385943BB-237E-4DA2-9A4A-4C2FB868E520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10BD8A02-8C8D-4900-953D-E59ECA79E9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C8E4A2-0D20-4D92-B9C0-B6707E90DD1B}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="26">
   <si>
     <t>場地費</t>
   </si>
@@ -260,10 +260,6 @@
       </rPr>
       <t>林小君</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>強哥</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6901,7 +6897,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45E352B3-6657-46BB-B44D-DB793939B652}">
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.5" style="5" bestFit="1" customWidth="1"/>
@@ -6959,7 +6955,7 @@
         <v>46266</v>
       </c>
       <c r="D3" s="25">
-        <f t="shared" ref="D3:D66" ca="1" si="0">10-ROUNDUP((TODAY()-$C3)/7,0)</f>
+        <f t="shared" ref="D3" ca="1" si="0">10-ROUNDUP((TODAY()-$C3)/7,0)</f>
         <v>5</v>
       </c>
       <c r="E3" s="26">
@@ -6967,1408 +6963,16 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24">
-        <v>46210</v>
-      </c>
-      <c r="D4" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-3</v>
-      </c>
-      <c r="E4" s="26">
-        <f ca="1">D4</f>
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E5" s="26">
-        <f ca="1">D5</f>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A6" s="6"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E6" s="26">
-        <f t="shared" ref="E6:E69" ca="1" si="1">D6</f>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A7" s="6"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E7" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A8" s="6"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E8" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A9" s="6"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E9" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A10" s="6"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E10" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A11" s="6"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E11" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A12" s="6"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E12" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A13" s="6"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E13" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A14" s="6"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E14" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A15" s="6"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E15" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A16" s="6"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E16" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A17" s="6"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E17" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A18" s="6"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E18" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A19" s="6"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E19" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A20" s="6"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E20" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A21" s="6"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E21" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A22" s="6"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E22" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A23" s="6"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E23" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A24" s="6"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E24" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A25" s="6"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E25" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A26" s="6"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E26" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A27" s="6"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E27" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A28" s="6"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E28" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A29" s="6"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E29" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A30" s="6"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E30" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A31" s="6"/>
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E31" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A32" s="6"/>
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E32" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A33" s="6"/>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E33" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A34" s="6"/>
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E34" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A35" s="6"/>
-      <c r="B35" s="24"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E35" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A36" s="6"/>
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E36" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A37" s="6"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E37" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A38" s="6"/>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E38" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A39" s="6"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E39" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A40" s="6"/>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E40" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A41" s="6"/>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E41" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A42" s="6"/>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E42" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A43" s="6"/>
-      <c r="B43" s="24"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E43" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A44" s="6"/>
-      <c r="B44" s="24"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E44" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A45" s="6"/>
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E45" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A46" s="6"/>
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E46" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A47" s="6"/>
-      <c r="B47" s="24"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E47" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A48" s="6"/>
-      <c r="B48" s="24"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E48" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A49" s="6"/>
-      <c r="B49" s="24"/>
-      <c r="C49" s="24"/>
-      <c r="D49" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E49" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A50" s="6"/>
-      <c r="B50" s="24"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E50" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A51" s="6"/>
-      <c r="B51" s="24"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E51" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A52" s="6"/>
-      <c r="B52" s="24"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E52" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A53" s="6"/>
-      <c r="B53" s="24"/>
-      <c r="C53" s="24"/>
-      <c r="D53" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E53" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A54" s="6"/>
-      <c r="B54" s="24"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E54" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A55" s="6"/>
-      <c r="B55" s="24"/>
-      <c r="C55" s="24"/>
-      <c r="D55" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E55" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A56" s="6"/>
-      <c r="B56" s="24"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E56" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A57" s="6"/>
-      <c r="B57" s="24"/>
-      <c r="C57" s="24"/>
-      <c r="D57" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E57" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A58" s="6"/>
-      <c r="B58" s="24"/>
-      <c r="C58" s="24"/>
-      <c r="D58" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E58" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A59" s="6"/>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E59" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A60" s="6"/>
-      <c r="B60" s="24"/>
-      <c r="C60" s="24"/>
-      <c r="D60" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E60" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A61" s="6"/>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E61" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A62" s="6"/>
-      <c r="B62" s="24"/>
-      <c r="C62" s="24"/>
-      <c r="D62" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E62" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A63" s="6"/>
-      <c r="B63" s="24"/>
-      <c r="C63" s="24"/>
-      <c r="D63" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E63" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A64" s="6"/>
-      <c r="B64" s="24"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E64" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A65" s="6"/>
-      <c r="B65" s="24"/>
-      <c r="C65" s="24"/>
-      <c r="D65" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E65" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A66" s="6"/>
-      <c r="B66" s="24"/>
-      <c r="C66" s="24"/>
-      <c r="D66" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>-6604</v>
-      </c>
-      <c r="E66" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A67" s="6"/>
-      <c r="B67" s="24"/>
-      <c r="C67" s="24"/>
-      <c r="D67" s="25">
-        <f t="shared" ref="D67:D110" ca="1" si="2">10-ROUNDUP((TODAY()-$C67)/7,0)</f>
-        <v>-6604</v>
-      </c>
-      <c r="E67" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A68" s="6"/>
-      <c r="B68" s="24"/>
-      <c r="C68" s="24"/>
-      <c r="D68" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E68" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A69" s="6"/>
-      <c r="B69" s="24"/>
-      <c r="C69" s="24"/>
-      <c r="D69" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E69" s="26">
-        <f t="shared" ca="1" si="1"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A70" s="6"/>
-      <c r="B70" s="24"/>
-      <c r="C70" s="24"/>
-      <c r="D70" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E70" s="26">
-        <f t="shared" ref="E70:E113" ca="1" si="3">D70</f>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A71" s="6"/>
-      <c r="B71" s="24"/>
-      <c r="C71" s="24"/>
-      <c r="D71" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E71" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A72" s="6"/>
-      <c r="B72" s="24"/>
-      <c r="C72" s="24"/>
-      <c r="D72" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E72" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A73" s="6"/>
-      <c r="B73" s="24"/>
-      <c r="C73" s="24"/>
-      <c r="D73" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E73" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A74" s="6"/>
-      <c r="B74" s="24"/>
-      <c r="C74" s="24"/>
-      <c r="D74" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E74" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A75" s="6"/>
-      <c r="B75" s="24"/>
-      <c r="C75" s="24"/>
-      <c r="D75" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E75" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A76" s="6"/>
-      <c r="B76" s="24"/>
-      <c r="C76" s="24"/>
-      <c r="D76" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E76" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A77" s="6"/>
-      <c r="B77" s="24"/>
-      <c r="C77" s="24"/>
-      <c r="D77" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E77" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A78" s="6"/>
-      <c r="B78" s="24"/>
-      <c r="C78" s="24"/>
-      <c r="D78" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E78" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A79" s="6"/>
-      <c r="B79" s="24"/>
-      <c r="C79" s="24"/>
-      <c r="D79" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E79" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A80" s="6"/>
-      <c r="B80" s="24"/>
-      <c r="C80" s="24"/>
-      <c r="D80" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E80" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A81" s="6"/>
-      <c r="B81" s="24"/>
-      <c r="C81" s="24"/>
-      <c r="D81" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E81" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A82" s="6"/>
-      <c r="B82" s="24"/>
-      <c r="C82" s="24"/>
-      <c r="D82" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E82" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A83" s="6"/>
-      <c r="B83" s="24"/>
-      <c r="C83" s="24"/>
-      <c r="D83" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E83" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A84" s="6"/>
-      <c r="B84" s="24"/>
-      <c r="C84" s="24"/>
-      <c r="D84" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E84" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A85" s="6"/>
-      <c r="B85" s="24"/>
-      <c r="C85" s="24"/>
-      <c r="D85" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E85" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A86" s="6"/>
-      <c r="B86" s="24"/>
-      <c r="C86" s="24"/>
-      <c r="D86" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E86" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A87" s="6"/>
-      <c r="B87" s="24"/>
-      <c r="C87" s="24"/>
-      <c r="D87" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E87" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A88" s="6"/>
-      <c r="B88" s="24"/>
-      <c r="C88" s="24"/>
-      <c r="D88" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E88" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A89" s="6"/>
-      <c r="B89" s="24"/>
-      <c r="C89" s="24"/>
-      <c r="D89" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E89" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A90" s="6"/>
-      <c r="B90" s="24"/>
-      <c r="C90" s="24"/>
-      <c r="D90" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E90" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A91" s="6"/>
-      <c r="B91" s="24"/>
-      <c r="C91" s="24"/>
-      <c r="D91" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E91" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A92" s="6"/>
-      <c r="B92" s="24"/>
-      <c r="C92" s="24"/>
-      <c r="D92" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E92" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A93" s="6"/>
-      <c r="B93" s="24"/>
-      <c r="C93" s="24"/>
-      <c r="D93" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E93" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A94" s="6"/>
-      <c r="B94" s="24"/>
-      <c r="C94" s="24"/>
-      <c r="D94" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E94" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A95" s="6"/>
-      <c r="B95" s="24"/>
-      <c r="C95" s="24"/>
-      <c r="D95" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E95" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A96" s="6"/>
-      <c r="B96" s="24"/>
-      <c r="C96" s="24"/>
-      <c r="D96" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E96" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A97" s="6"/>
-      <c r="B97" s="24"/>
-      <c r="C97" s="24"/>
-      <c r="D97" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E97" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A98" s="6"/>
-      <c r="B98" s="24"/>
-      <c r="C98" s="24"/>
-      <c r="D98" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E98" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A99" s="6"/>
-      <c r="B99" s="24"/>
-      <c r="C99" s="24"/>
-      <c r="D99" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E99" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A100" s="6"/>
-      <c r="B100" s="24"/>
-      <c r="C100" s="24"/>
-      <c r="D100" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E100" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A101" s="6"/>
-      <c r="B101" s="24"/>
-      <c r="C101" s="24"/>
-      <c r="D101" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E101" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A102" s="6"/>
-      <c r="B102" s="24"/>
-      <c r="C102" s="24"/>
-      <c r="D102" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E102" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A103" s="6"/>
-      <c r="B103" s="24"/>
-      <c r="C103" s="24"/>
-      <c r="D103" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E103" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A104" s="6"/>
-      <c r="B104" s="24"/>
-      <c r="C104" s="24"/>
-      <c r="D104" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E104" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A105" s="6"/>
-      <c r="B105" s="24"/>
-      <c r="C105" s="24"/>
-      <c r="D105" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E105" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A106" s="6"/>
-      <c r="B106" s="24"/>
-      <c r="C106" s="24"/>
-      <c r="D106" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E106" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A107" s="6"/>
-      <c r="B107" s="24"/>
-      <c r="C107" s="24"/>
-      <c r="D107" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E107" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A108" s="6"/>
-      <c r="B108" s="24"/>
-      <c r="C108" s="24"/>
-      <c r="D108" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E108" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A109" s="6"/>
-      <c r="B109" s="24"/>
-      <c r="C109" s="24"/>
-      <c r="D109" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E109" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A110" s="6"/>
-      <c r="B110" s="24"/>
-      <c r="C110" s="24"/>
-      <c r="D110" s="25">
-        <f t="shared" ca="1" si="2"/>
-        <v>-6604</v>
-      </c>
-      <c r="E110" s="26">
-        <f t="shared" ca="1" si="3"/>
-        <v>-6604</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{7D892569-22EB-494F-B195-8AE49997C515}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="E2:E110">
-    <cfRule type="iconSet" priority="4">
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E3">
+    <cfRule type="iconSet" priority="5">
       <iconSet iconSet="4TrafficLights" showValue="0">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="0" gte="0"/>
@@ -8377,11 +6981,6 @@
       </iconSet>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/For Streamlit.xlsx
+++ b/For Streamlit.xlsx
@@ -764,7 +764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,22 +821,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>強哥</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/For Streamlit.xlsx
+++ b/For Streamlit.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="收支明細" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="季繳名單" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="每周收支" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="季繳追蹤" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,7 +455,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46266</v>
+        <v>46294</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -472,14 +472,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>齊</t>
+          <t>妙</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46266</v>
+        <v>46294</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -492,18 +492,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3750</v>
+        <v>2550</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>櫃台</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1hr*2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46273</v>
+        <v>46294</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -512,74 +516,70 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>羽毛球</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1520</v>
+        <v>990</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>妙</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46273</v>
+        <v>46287</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2900</v>
+        <v>760</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>櫃台</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1hr*1</t>
-        </is>
-      </c>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1520</v>
+        <v>500</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>妙</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -588,163 +588,163 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>季繳</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>櫃台</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>轉帳 (冠臻)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>季繳</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2200</v>
+        <v>1520</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>妙</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>轉帳 (冠臻)</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46287</v>
+        <v>46280</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>760</v>
+        <v>2500</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>妙</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46287</v>
+        <v>46273</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>500</v>
+        <v>1520</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>妙</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46294</v>
+        <v>46273</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1520</v>
+        <v>2900</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>妙</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1hr*1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46294</v>
+        <v>46266</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2550</v>
+        <v>1520</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>櫃台</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1hr*2</t>
-        </is>
-      </c>
+          <t>齊</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46294</v>
+        <v>46266</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>羽毛球</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>990</v>
+        <v>3750</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>

--- a/For Streamlit.xlsx
+++ b/For Streamlit.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,7 +455,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -464,18 +464,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>活動費</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1520</v>
+        <v>2000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>妙</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>範例</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -483,27 +487,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2550</v>
+        <v>1520</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>櫃台</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1hr*2</t>
-        </is>
-      </c>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -511,27 +511,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>羽毛球</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>990</v>
+        <v>2550</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>櫃台</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1hr*2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -540,15 +544,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>羽毛球</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>760</v>
+        <v>990</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>妙</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -559,27 +563,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>500</v>
+        <v>760</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>妙</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -588,46 +592,46 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>季繳</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2200</v>
+        <v>500</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>妙</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>轉帳 (冠臻)</t>
-        </is>
-      </c>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>季繳</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1520</v>
+        <v>2200</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>妙</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>轉帳 (冠臻)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -635,44 +639,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2500</v>
+        <v>1520</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>妙</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1520</v>
+        <v>2500</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>妙</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -683,51 +687,51 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2900</v>
+        <v>1520</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>櫃台</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1hr*1</t>
-        </is>
-      </c>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1520</v>
+        <v>2900</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>齊</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1hr*1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -735,23 +739,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>場地費</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1520</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>齊</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>臨打</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D14" t="n">
         <v>3750</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>櫃台</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -764,7 +792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,6 +849,22 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>小明</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
